--- a/DATA/MODELADO/Diagnosticos/Exp01-V3/diagnostico_modelo_Exp01-V3.xlsx
+++ b/DATA/MODELADO/Diagnosticos/Exp01-V3/diagnostico_modelo_Exp01-V3.xlsx
@@ -453,7 +453,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0.9103</t>
+          <t>0.9487</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -487,12 +487,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.4167</t>
+          <t>0.6667</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -504,7 +504,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0.5882</t>
+          <t>0.8000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -538,7 +538,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -555,7 +555,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>MODELO APROBADO</t>
+          <t>Excelente</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
